--- a/discourse_chinese_mixed_sorted_summary.xlsx
+++ b/discourse_chinese_mixed_sorted_summary.xlsx
@@ -3042,7 +3042,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>2.33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3120,14 +3120,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3691,18 +3691,18 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.73</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3723,14 +3723,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3747,18 +3747,18 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3775,18 +3775,18 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3794,27 +3794,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3822,27 +3822,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>军事基地</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3859,18 +3859,18 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3887,18 +3887,18 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3915,18 +3915,18 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3934,27 +3934,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3971,18 +3971,18 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3990,27 +3990,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>可持续发展</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>透明度</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>马六甲困境</t>
+          <t>零和博弈</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4087,14 +4087,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -4111,18 +4111,18 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4167,18 +4167,18 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4195,18 +4195,18 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -4214,27 +4214,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -4242,27 +4242,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -4279,18 +4279,18 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>军事基地</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4307,18 +4307,18 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>透明度</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4335,18 +4335,18 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -4354,27 +4354,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>军事化</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4391,18 +4391,18 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -4410,27 +4410,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>可持续发展</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4479,14 +4479,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>零和博弈</t>
+          <t>马六甲困境</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>

--- a/discourse_chinese_mixed_sorted_summary.xlsx
+++ b/discourse_chinese_mixed_sorted_summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -505,7 +505,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -525,7 +525,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -545,7 +545,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -585,11 +585,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>命运共同体</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -625,11 +625,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -645,11 +645,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -665,7 +665,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -685,11 +685,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -705,11 +705,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -725,7 +725,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -745,11 +745,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -760,16 +760,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -780,16 +780,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -800,12 +800,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>共同繁荣</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -865,11 +865,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -880,12 +880,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -920,12 +920,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>经济繁荣</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -940,12 +940,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>债务危机</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -980,12 +980,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>债务负担</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1000,16 +1000,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>缺乏透明度</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>零和博弈</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1080,16 +1080,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1100,16 +1100,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>共同繁荣</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>和平与发展</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>区域一体化</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1235,17 +1235,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>零和博弈</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1255,87 +1255,87 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>早期收获</t>
+          <t>军事基地</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>军民两用</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1355,7 +1355,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1375,7 +1375,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>就业创造</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1395,7 +1395,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1405,27 +1405,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>脱贫</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1435,7 +1435,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1469,33 +1469,33 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>剥夺</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>环境破坏</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1605,11 +1605,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1620,16 +1620,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>早期收获</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>马六甲困境</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1665,11 +1665,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1685,11 +1685,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1740,16 +1740,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1760,16 +1760,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>命运共同体</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>合作共赢</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1805,37 +1805,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>区域一体化</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1855,7 +1855,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1895,17 +1895,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>早期收获</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -1915,7 +1915,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1925,27 +1925,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>减贫</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1955,27 +1955,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>债务负担</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1995,7 +1995,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>经济繁荣</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2035,37 +2035,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2075,37 +2075,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>主权争议</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2115,7 +2115,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>马六甲困境</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2135,7 +2135,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2145,57 +2145,57 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>共同繁荣</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2235,17 +2235,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>全球发展倡议</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2255,57 +2255,57 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>军事基地</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>安全威胁</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2315,7 +2315,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2335,17 +2335,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>零和博弈</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2355,17 +2355,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2375,7 +2375,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2385,31 +2385,31 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>剥夺</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>环境破坏</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2420,16 +2420,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>早期收获</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>早期收获</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2515,7 +2515,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2545,17 +2545,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>可持续发展</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2575,7 +2575,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2635,7 +2635,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2645,17 +2645,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2665,17 +2665,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>债务负担</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>扩张工具</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -2695,37 +2695,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -2735,27 +2735,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Western_Realist</t>
+          <t>Chinese_Official</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>减贫</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>马六甲困境</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -2775,7 +2775,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>减贫</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -2815,7 +2815,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>经济繁荣</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -2835,7 +2835,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2845,17 +2845,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>安全威胁</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2865,27 +2865,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chinese_Official</t>
+          <t>Western_Realist</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>债务危机</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -2895,7 +2895,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>缺乏透明度</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2925,30 +2925,1110 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>珍珠链</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>债务危机</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>安全威胁</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>互联互通</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>全天候战略</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>共同发展</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>和平与发展</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>命运共同体</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>零和博弈</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>军事化</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>珍珠链</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>战略包围</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>资源掠夺</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>就业创造</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>早期收获</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>军事化</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>剥夺</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>环境破坏</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>不透明</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>ChatGPT</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>互联互通</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>互联互通</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>互利共赢</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>共同发展</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
         <is>
           <t>Western_Realist</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>债务陷阱</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>新殖民主义</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>扩张工具</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>经济繁荣</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>债务陷阱</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>债务危机</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>印太战略</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>马六甲困境</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>互联互通</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>全天候战略</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>和平与发展</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>命运共同体</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>军事基地</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>珍珠链</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>战略包围</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>军民两用</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>军事化</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>资源掠夺</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>改善民生</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Chinese_Official</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>就业创造</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>军事化</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>剥夺</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Western_Realist</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>环境破坏</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3005,14 +4085,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -3028,14 +4108,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -3051,14 +4131,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>2.33</v>
+        <v>3.06</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -3074,14 +4154,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -3097,14 +4177,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
     </row>
@@ -3120,14 +4200,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -3143,14 +4223,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -3166,14 +4246,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -3188,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3346,7 +4426,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>剥夺</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3355,11 +4435,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.26</t>
         </is>
       </c>
     </row>
@@ -3374,12 +4454,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3402,12 +4482,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3430,20 +4510,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
@@ -3458,12 +4538,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3486,7 +4566,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>共同繁荣</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3542,7 +4622,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3551,11 +4631,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -3570,20 +4650,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>早期收获</t>
+          <t>环境破坏</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -3598,7 +4678,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3607,11 +4687,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -3626,20 +4706,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -3654,35 +4734,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>马六甲困境</t>
+          <t>经济繁荣</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>减贫</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3691,82 +4771,82 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>共商共建</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>全天候战略</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Chinese Official (中)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>7</v>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>区域一体化</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>共商共建</t>
+          <t>全球发展倡议</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3775,26 +4855,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>命运共同体</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3803,54 +4883,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>合作共赢</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>早期收获</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3859,26 +4939,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>主权争议</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3887,26 +4967,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>债务负担</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3915,82 +4995,82 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>安全威胁</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>高质量发展</t>
+          <t>新殖民主义</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Doubao</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>马六甲困境</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3999,11 +5079,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
@@ -4014,11 +5094,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4027,11 +5107,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.73</t>
         </is>
       </c>
     </row>
@@ -4042,24 +5122,24 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>全天候战略</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
@@ -4070,11 +5150,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>零和博弈</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4083,26 +5163,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>互利共赢</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4111,50 +5191,50 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>旗舰项目</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4171,106 +5251,106 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>军事基地</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>印太战略</t>
+          <t>共商共建</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>印太战略</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>民生改善</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4279,26 +5359,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>军事基地</t>
+          <t>剥夺</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4307,82 +5387,82 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>改善民生</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>高质量发展</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>经济繁荣</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4391,138 +5471,138 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>可持续发展</t>
+          <t>珍珠链</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>环境破坏</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>共同繁荣</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>马六甲困境</t>
+          <t>共同发展</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>旗舰项目</t>
+          <t>和平与发展</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4531,54 +5611,54 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>透明度</t>
+          <t>区域一体化</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>全天候战略</t>
+          <t>就业创造</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4587,54 +5667,54 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新殖民主义</t>
+          <t>命运共同体</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Western Realist (西)</t>
+          <t>Chinese Official (中)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>互联互通</t>
+          <t>脱贫</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4643,54 +5723,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>民生改善</t>
+          <t>债务负担</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>债务陷阱</t>
+          <t>债务危机</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4699,26 +5779,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>军事化</t>
+          <t>军民两用</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4727,54 +5807,54 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>互利共赢</t>
+          <t>缺乏透明度</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Doubao</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>珍珠链</t>
+          <t>零和博弈</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4783,26 +5863,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>早期收获</t>
+          <t>互联互通</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4811,65 +5891,1437 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.57</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>命运共同体</t>
+          <t>债务陷阱</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Chinese Official (中)</t>
+          <t>Western Realist (西)</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>ChatGPT</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>新殖民主义</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>剥夺</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>印太战略</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>互利共赢</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>9</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>和平与发展</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>军事基地</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>11</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>军事化</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>12</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>债务危机</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
         <v>13</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>改善民生</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>14</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>全天候战略</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>15</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>就业创造</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>16</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>共同发展</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>17</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>命运共同体</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>18</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>军民两用</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>19</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>经济繁荣</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>20</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>战略包围</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>21</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>扩张工具</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>22</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>环境破坏</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>23</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>珍珠链</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>24</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>资源掠夺</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>25</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>马六甲困境</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>旗舰项目</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>全天候战略</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>互联互通</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>新殖民主义</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>民生改善</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>债务陷阱</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>减贫</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>军事化</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>早期收获</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>互利共赢</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>共同发展</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>12</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>珍珠链</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>13</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>缺乏透明度</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>14</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>环境破坏</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>15</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>债务危机</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>16</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>安全威胁</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>17</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>就业创造</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>18</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>命运共同体</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>19</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>和平与发展</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>20</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>剥夺</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>21</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>经济繁荣</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Chinese Official (中)</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>22</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>不透明</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>23</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>债务负担</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>24</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>战略包围</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>25</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>扩张工具</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>26</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>资源掠夺</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Western Realist (西)</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>27</v>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>零和博弈</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Western Realist (西)</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
